--- a/ARQUIVOS_GERADOS/BI_ABASTECIMENTO/OS_PD.xlsx
+++ b/ARQUIVOS_GERADOS/BI_ABASTECIMENTO/OS_PD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,35 +439,35 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B2" t="n">
-        <v>180185</v>
+        <v>122537</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B3" t="n">
-        <v>180921</v>
+        <v>180121</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B4" t="n">
-        <v>181012</v>
+        <v>180185</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -475,10 +475,10 @@
         <v>46133</v>
       </c>
       <c r="B5" t="n">
-        <v>36699</v>
+        <v>180815</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -486,10 +486,10 @@
         <v>46133</v>
       </c>
       <c r="B6" t="n">
-        <v>100080</v>
+        <v>181012</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -497,21 +497,21 @@
         <v>46133</v>
       </c>
       <c r="B7" t="n">
-        <v>180101</v>
+        <v>181169</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B8" t="n">
-        <v>180815</v>
+        <v>1260</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -519,10 +519,10 @@
         <v>46134</v>
       </c>
       <c r="B9" t="n">
-        <v>1260</v>
+        <v>26082</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -530,10 +530,10 @@
         <v>46134</v>
       </c>
       <c r="B10" t="n">
-        <v>100080</v>
+        <v>36699</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -541,10 +541,10 @@
         <v>46134</v>
       </c>
       <c r="B11" t="n">
-        <v>180101</v>
+        <v>100080</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -552,21 +552,98 @@
         <v>46134</v>
       </c>
       <c r="B12" t="n">
-        <v>180782</v>
+        <v>122537</v>
       </c>
       <c r="C12" t="n">
-        <v>846</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B13" t="n">
+        <v>180101</v>
+      </c>
+      <c r="C13" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B14" t="n">
+        <v>180185</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B15" t="n">
+        <v>180782</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B16" t="n">
+        <v>180815</v>
+      </c>
+      <c r="C16" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B17" t="n">
+        <v>181012</v>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B18" t="n">
+        <v>181169</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B19" t="n">
+        <v>180782</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
         <v>46133</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B20" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="n">
-        <v>57</v>
+      <c r="C20" t="n">
+        <v>351</v>
       </c>
     </row>
   </sheetData>
